--- a/output/full_scan/batch_seq4_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq4_2026-10-22.xlsx
@@ -444,7 +444,7 @@
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1164.905087320008</v>
+        <v>1164.905087320007</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>11.85</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.47402729952995</v>
+        <v>61.47402775815982</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>35.26102500936702</v>
+        <v>35.26102499764791</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>5.036995786246373</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.01603330018520389</v>
+        <v>0.01603330019922097</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>62.51548035642543</v>
+        <v>62.51548038061753</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33.15904655268275</v>
+        <v>33.15904665841565</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.604334558667896</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.96108387146009</v>
+        <v>1.961083869077171</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.63374880477039</v>
+        <v>67.63374897056346</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>13.68846345550748</v>
+        <v>13.68846350727148</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>8.002482972571181</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1182928653352644</v>
+        <v>0.1182928653492785</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>58.97534197016448</v>
+        <v>58.97534219430216</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>32.52770021573721</v>
+        <v>32.52770033783371</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.053526897830448</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.06169077719380767</v>
+        <v>0.06169077709568782</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>70.40003971099242</v>
+        <v>70.40003988304316</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19.31790238040283</v>
+        <v>19.31790244059673</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>7.21843596962063</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.09789239286415433</v>
+        <v>0.09789239259783132</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>58.53467319629787</v>
+        <v>58.53467328779068</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>35.41628345546611</v>
+        <v>35.41628388395351</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.6332579594761804</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.08769978997779804</v>
+        <v>0.08769978956941671</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>49.97994031636121</v>
+        <v>49.97994027225257</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>24.51152216883556</v>
+        <v>24.511522195827</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.9222269348454117</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.6419983724512575</v>
+        <v>-0.6419983723671492</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>823.4509602620203</v>
+        <v>823.4509602620202</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>138</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>63.33650972574698</v>
+        <v>63.33650951944309</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>31.65229995058348</v>
+        <v>31.65230004845873</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.9703295411600992</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4836087041487165</v>
+        <v>0.4836087045692197</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>68.36121922026462</v>
+        <v>68.36121925499614</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>29.67399962410031</v>
+        <v>29.67399966123428</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>0.6036744279557782</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.447818001513143</v>
+        <v>1.447818001372949</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>784.0790973165975</v>
+        <v>784.0790973165969</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>20.75</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>70.34510545784933</v>
+        <v>70.34510544221374</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.3270205870358</v>
+        <v>26.32702054254613</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.088563141695154</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1219342258591189</v>
+        <v>0.1219342258731374</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>52.48283290166222</v>
+        <v>52.48283290526659</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>28.72599747100166</v>
+        <v>28.72599769809614</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.033829281665624</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-13.21008645516991</v>
+        <v>-13.21008645559044</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>53.63570805431231</v>
+        <v>53.63570807456691</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38.57695159006221</v>
+        <v>38.57695159645509</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.2833946906944184</v>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>773.4437123179023</v>
+        <v>773.4437123179022</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>190</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>53.91634620797773</v>
+        <v>53.91634619997794</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>18.49676036178668</v>
+        <v>18.49676037598203</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.8614370201763466</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3811123268596368</v>
+        <v>0.3811123269998309</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>54.88926146910697</v>
+        <v>54.88926163909885</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>26.29987375808416</v>
+        <v>26.29987381544195</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.8892348881252753</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.6321526699167506</v>
+        <v>0.6321526689355563</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>52.70254201681706</v>
+        <v>52.702542018731</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.28902191026091</v>
+        <v>22.28902191026092</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.943164989278573</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-6.054385274754544</v>
+        <v>-6.05438527461439</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>742.0820111951988</v>
+        <v>742.082011195199</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>73</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>53.93914779951866</v>
+        <v>53.93914782477416</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24.21820690881158</v>
+        <v>24.21820699793755</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>2.536382284830192</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.2954901498022551</v>
+        <v>-0.2954901498723292</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>735.812365644895</v>
+        <v>735.8123656448948</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>406</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>44.61651164530582</v>
+        <v>44.61651164950867</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>27.7317525216467</v>
+        <v>27.73175253060018</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.8918892127847367</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-10.0063853129032</v>
+        <v>-10.00638531298729</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>735.0980467841543</v>
+        <v>735.0980467841542</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>52</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.97981351897392</v>
+        <v>55.97981354772426</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>33.56418745138104</v>
+        <v>33.56418756549992</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.6708021760825953</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.4426517984956631</v>
+        <v>-0.4426517986218212</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>68.12648078309954</v>
+        <v>68.1264808050847</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24.96682628172807</v>
+        <v>24.96682637976815</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.883170206659643</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>55.85654003290239</v>
+        <v>55.8565406759719</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>28.73091869982559</v>
+        <v>28.73091884881891</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.988191331580517</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.6906946178034366</v>
+        <v>0.6906946158410259</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>48.25581713151513</v>
+        <v>48.25581759728188</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21.43317875552836</v>
+        <v>21.43317877491759</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.8865828487542543</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4668011084315532</v>
+        <v>0.4668011075905196</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.0198092136724</v>
+        <v>55.01980925467333</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>41.20888385737582</v>
+        <v>41.20888387451155</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.468848032768538</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-2.412279578055454</v>
+        <v>-2.412279578504005</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.87964625357978</v>
+        <v>56.8796462987446</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>11.51777447892558</v>
+        <v>11.51777485147745</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>4.687041380826769</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.06959488648152769</v>
+        <v>0.06959488643947602</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>58.86706062866943</v>
+        <v>58.86706064028974</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>48.50117160937236</v>
+        <v>48.50117173456443</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.203127899167529</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.9592619924512586</v>
+        <v>-0.9592619926475052</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>685.7898084125552</v>
+        <v>685.7898084125553</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>99.40000000000001</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>63.43843914902461</v>
+        <v>63.60839440645645</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>60.82606807256959</v>
+        <v>60.86792432348801</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.9653194621989537</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0528528617409964</v>
+        <v>-0.05289005527878765</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>684.4945653665075</v>
+        <v>684.4945653665073</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>53.3</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>62.11978058203621</v>
+        <v>62.11978071629139</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>22.34181026496895</v>
+        <v>22.34181026816069</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>2.252029936868723</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.3475974135070516</v>
+        <v>0.347597413394914</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>69.1620928033161</v>
+        <v>69.16209285629361</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>52.61033190302032</v>
+        <v>52.61033144194509</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.3033893816136366</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.09282376809640303</v>
+        <v>-0.09282376813964499</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.30008147893226</v>
+        <v>54.30008160794988</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>37.24091353842664</v>
+        <v>37.24091371619389</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.3450147899488127</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.21103533320547</v>
+        <v>-0.2110353333496062</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>60.64081896595285</v>
+        <v>60.64081871543931</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>22.78810846713945</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.2629897801384203</v>
+        <v>0.262989780222515</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.83531498827519</v>
+        <v>58.83531502707721</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26.3513443458831</v>
+        <v>26.351344485566</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1.122992628602494</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.2584999352921207</v>
+        <v>-0.2584999355163911</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>637.532524698246</v>
+        <v>637.5325246982458</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>134.5</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>54.60391550313163</v>
+        <v>54.60391563743473</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>31.98525608109448</v>
+        <v>31.98525638732931</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.91347036069911</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.3506029232786285</v>
+        <v>-0.3506029255213501</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>52.31734292237829</v>
+        <v>52.31734294674902</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>47.22762787134751</v>
+        <v>47.22762787706826</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>1.500737638636496</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.7888440009987754</v>
+        <v>-0.7888440012790667</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>61.51364417959146</v>
+        <v>61.51364430105911</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>39.12660037163083</v>
+        <v>39.12660043090043</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.9970059574653023</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0942997991648743</v>
+        <v>0.09429979899667035</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>32.46600685368614</v>
+        <v>32.46600707796276</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>37.53584052752785</v>
+        <v>37.53584046653628</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1.768066487666728</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-1.15632413340218</v>
+        <v>-1.156324133009702</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>50.68495985885134</v>
+        <v>50.68495986592747</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30.48649512525034</v>
+        <v>30.48649516391101</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1.081929049966906</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-149.3271173359768</v>
+        <v>-149.3271173429845</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.2542581551089</v>
+        <v>54.25425817659968</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10.37893435020889</v>
+        <v>10.37893433862846</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1.342719226506336</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.01806480480558054</v>
+        <v>-0.01806480483361339</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45.30827755388852</v>
+        <v>45.30827768130075</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>41.4004622454517</v>
+        <v>41.40046244033326</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.7014763321774579</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-3.614971131383276</v>
+        <v>-3.614971131775746</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>575.0319520460725</v>
+        <v>575.0319520460733</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>246.5</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>48.1658398073676</v>
+        <v>48.16583982737636</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>26.61512167048243</v>
+        <v>26.61512172022451</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>1.101112150690772</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-1.94972577832581</v>
+        <v>-1.949725778465964</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>49.3655668754953</v>
+        <v>49.36556686211038</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>50.46100169822061</v>
+        <v>50.4610017616477</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.8209166950979533</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.8234747509672555</v>
+        <v>-0.8234747509111848</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>56.1086559026057</v>
+        <v>56.10865578775991</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>44.30923842228178</v>
+        <v>44.30923843455429</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.4553682703126941</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.03744107218149417</v>
+        <v>-0.03744107198525581</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>65.01408151316778</v>
+        <v>65.01408150215795</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>61.23499220201322</v>
+        <v>61.23499220368753</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.4325390849572122</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.7550942321179228</v>
+        <v>0.7550942322020262</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>64.02061414236809</v>
+        <v>64.0206141744857</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>38.05934382194233</v>
+        <v>38.0593437988155</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>2.355594892473223</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1.163937035741685</v>
+        <v>1.163937035881854</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.63200286012541</v>
+        <v>55.63200296126468</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>31.53857181088594</v>
+        <v>31.53857181611926</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.9255862855234631</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.01286565966755326</v>
+        <v>0.01286565972362397</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>47.59751815068772</v>
+        <v>47.59751827572224</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>23.79872277794786</v>
+        <v>23.79872281600989</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.5264611653708209</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.59142137535142</v>
+        <v>51.5914213701638</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45.75323321631652</v>
+        <v>45.75323322183514</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1.34955005848582</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1599137977763003</v>
+        <v>-0.1599137977903182</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>550.4416935965256</v>
+        <v>550.4416935965253</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>28.25</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.16390627187491</v>
+        <v>52.1639066543557</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>41.03664221515627</v>
+        <v>41.03664239751886</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.8422910835377824</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.09360325351751919</v>
+        <v>0.09360325312504214</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>68.85010892908463</v>
+        <v>68.85010888610475</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>30.69209827731894</v>
+        <v>30.69209822271302</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.758740999564794</v>
@@ -3029,7 +3029,7 @@
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>525.2393373712024</v>
+        <v>525.2393373712025</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>112.5</v>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45.32206157245741</v>
+        <v>45.32206176616827</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>25.58170862643406</v>
+        <v>25.5817086002088</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>1.375234090168809</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.2523220474491543</v>
+        <v>-0.2523220480098538</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.30282472104496</v>
+        <v>49.30282451330446</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>31.61073967236726</v>
+        <v>31.61073969288005</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.06572529108323961</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.01830271897578611</v>
+        <v>0.01830271914399109</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>56.10045249068143</v>
+        <v>56.10045257230613</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.8086566983771</v>
+        <v>25.80865673684696</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1.753245980885995</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1131683395865977</v>
+        <v>0.113168339530531</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>516.9612415171518</v>
+        <v>516.9612415171516</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>654</v>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43.97944515931698</v>
+        <v>43.97944515471536</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21.26288529429356</v>
+        <v>21.26288523975834</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.143651119728604</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-11.50342797476457</v>
+        <v>-11.50342797448426</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>43.30923086882766</v>
+        <v>43.30923091776108</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>29.96734989938802</v>
+        <v>29.96734997489351</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>1.106612968242505</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.05956377380315533</v>
+        <v>-0.059563773845207</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>40.63302884494458</v>
+        <v>40.63302816025924</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>32.49664593809712</v>
+        <v>32.49664606599941</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.7037498837337249</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.1835629124798766</v>
+        <v>-0.183562912521926</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>506.9306963161364</v>
+        <v>506.930696316136</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>50.1</v>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49.30370112705953</v>
+        <v>49.30370114126904</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.87621149795592</v>
+        <v>12.87621158006379</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>3.330882068176479</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.05867847366507556</v>
+        <v>-0.05867847393140635</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>53.34072370223447</v>
+        <v>53.34072374424331</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>37.07152884581713</v>
+        <v>37.07152912896473</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.5559023809113054</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1566820006330445</v>
+        <v>-0.1566820009414203</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>33.59922693518726</v>
+        <v>33.59922646657392</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>28.3671148580892</v>
+        <v>28.36711500662524</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.9241175372373642</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.08337383530844067</v>
+        <v>0.0833738354486091</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45.68033969728566</v>
+        <v>45.68033958016738</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>34.85111895707984</v>
+        <v>34.85111888630085</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.2613527511227026</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.09320782274355618</v>
+        <v>-0.09320782265945426</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>42.73405368193763</v>
+        <v>42.73405370561109</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>25.34767419122422</v>
+        <v>25.3476742929033</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.493929363935769</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-8.820259599780833</v>
+        <v>-8.820259601462965</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>56.56294254291823</v>
+        <v>56.56294261185521</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.95003281916447</v>
+        <v>16.95003286552277</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.227449937353827</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.2690720357255969</v>
+        <v>-0.2690720356415002</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.24669485715717</v>
+        <v>39.24669498992057</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.90642064635253</v>
+        <v>15.90642063462829</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.6407344539018502</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-53.29848650710696</v>
+        <v>-53.29848652673049</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40.26446686146063</v>
+        <v>40.26446709995366</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>23.92963754088822</v>
+        <v>23.92963758892055</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.753484012359796</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.481660957826936</v>
+        <v>-0.4816609596491388</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>64.36089812050996</v>
+        <v>64.36089812982834</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.51804668950422</v>
+        <v>12.51804669475725</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>1.91046619079405</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.6253669568214565</v>
+        <v>0.6253669568022382</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>486.5989112411499</v>
+        <v>486.5989112411505</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>80.5</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.6829540919935</v>
+        <v>43.68295450103754</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.41846827705995</v>
+        <v>14.41846839069087</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.6559266313997792</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.2754521542449624</v>
+        <v>0.2754521526750775</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.84831727078033</v>
+        <v>45.84831733590165</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>41.31549924615111</v>
+        <v>41.31549941712537</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.3627913678335234</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.303749945636224</v>
+        <v>-1.303749945720327</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>483.166165873248</v>
+        <v>483.1661658732478</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>25.85</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.1597970924214</v>
+        <v>44.15979726171204</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>32.06275654059851</v>
+        <v>32.06275719420422</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.7290753412003399</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.5084100600599928</v>
+        <v>-0.5084100605085337</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.38982751717008</v>
+        <v>52.38982753170786</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>52.11647752339608</v>
+        <v>52.11647758623981</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>1.400901201073391</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-3.435925738023293</v>
+        <v>-3.435925738037319</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>480.0369351556326</v>
+        <v>480.0369351556325</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>62.4</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>42.29365673661103</v>
+        <v>42.29365697117156</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>20.99423467204613</v>
+        <v>20.99423473976882</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.2741201903557642</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.7908029660569523</v>
+        <v>-0.7908029665615691</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.82674984155623</v>
+        <v>49.82674983213288</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14.90201794724318</v>
+        <v>14.9020179071343</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>1.367714314379494</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1072755306452651</v>
+        <v>0.1072755307153299</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>53.36246438736696</v>
+        <v>53.36246442821943</v>
       </c>
       <c r="I70" s="2" t="n">
         <v>26.24846264790846</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.05615641760580692</v>
+        <v>0.05615641761982341</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>477.2855844299168</v>
+        <v>477.285584429917</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>54.5</v>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.87548041109164</v>
+        <v>50.87548045308355</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46.42601396692774</v>
+        <v>46.42601403742662</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.8737095348432393</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.6634027269804692</v>
+        <v>-0.6634027272467904</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>475.6569599045382</v>
+        <v>475.6569599045383</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>6070</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>42.88151852165817</v>
+        <v>42.88151857732991</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>26.5729269053418</v>
+        <v>26.5729269758017</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>1.335685295786755</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-141.2375978608678</v>
+        <v>-141.2375978804924</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.66746730949686</v>
+        <v>47.6674672164571</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>38.08662991754114</v>
+        <v>38.08662994974759</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.7079444480678945</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.5980695286250762</v>
+        <v>0.5980695290455816</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>42.9840283779867</v>
+        <v>42.9840283897007</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>27.58863498421758</v>
+        <v>27.58863505857138</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.5499819022405972</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-4.836267380227167</v>
+        <v>-4.836267380647712</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.53274374856134</v>
+        <v>44.53274389695279</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>31.24306729749201</v>
+        <v>31.24306720831868</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.2378090188967205</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.695770758549551</v>
+        <v>-1.695770758717753</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.28761533298571</v>
+        <v>49.28761534406029</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>33.53521210239691</v>
+        <v>33.53521222938689</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.8676045168962995</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.4076498808463946</v>
+        <v>-0.407649880888445</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>44.08328591783778</v>
+        <v>44.08328592038442</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.1839876277018</v>
+        <v>18.18398753447466</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.5035917826125005</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.57681796951262</v>
+        <v>42.57681798041673</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.7636253072819</v>
+        <v>19.76362533512224</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.435378369192445</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.4594548904613531</v>
+        <v>-0.4594548905594675</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>49.18621357081179</v>
+        <v>49.1862135440285</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>39.96661509884778</v>
+        <v>39.96661510763369</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.4546082140593823</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.9453302706716791</v>
+        <v>-0.9453302705735589</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.03081122759576</v>
+        <v>42.03081092302644</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20.87469674397181</v>
+        <v>20.87469727726448</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.4561618683699927</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.2908459607733261</v>
+        <v>-0.2908459600724737</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>450.8933079648536</v>
+        <v>450.8933079648535</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>23.5</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.97835683328564</v>
+        <v>47.97835698049823</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>26.06429529781598</v>
+        <v>26.06429533048161</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.6209555385465898</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.176681609204163</v>
+        <v>-0.1766816092882632</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>47.85557392898946</v>
+        <v>47.85557393680818</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>30.8632961289848</v>
+        <v>30.863296353856</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.8488007396211577</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-4.014590889112775</v>
+        <v>-4.014590889280996</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>445.1000265277706</v>
+        <v>445.1000265277709</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>328</v>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>26.96541280096397</v>
+        <v>26.96541285114976</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>25.55255241512142</v>
+        <v>25.55255243890391</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.8950799796452875</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-3.462316180221784</v>
+        <v>-3.46231618036196</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>444.5135920382036</v>
+        <v>444.5135920382035</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>221.5</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>51.81978004801427</v>
+        <v>51.81978005120514</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>23.0505493761388</v>
+        <v>23.05054937647085</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>1.630424828909177</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.9218772312721408</v>
+        <v>0.921877230991782</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.96830578638225</v>
+        <v>50.96830577403114</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>4.975788512461391</v>
+        <v>4.975788558239763</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.365218089982433</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.03346174998688956</v>
+        <v>-0.03346174983270156</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>436.5693363942286</v>
+        <v>436.5693363942289</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>62.7</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>46.26635614649758</v>
+        <v>46.26635617846141</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>23.50039274141508</v>
+        <v>23.5003927815248</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.679557348313885</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1303730428222107</v>
+        <v>0.1303730426540126</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>435.0558891660842</v>
+        <v>435.0558891660838</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>63.5</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.88542952977618</v>
+        <v>51.88542953299229</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8.479029646655766</v>
+        <v>8.479029865189892</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>1.052517850432168</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.2273961011730594</v>
+        <v>-0.2273961019860447</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>431.1193481102929</v>
+        <v>431.1193481102932</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>60.9</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>48.89346399282474</v>
+        <v>48.89346408729898</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.85266033228001</v>
+        <v>18.85266041188761</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.5792006061559767</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.05511606842364536</v>
+        <v>0.05511606819937664</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>40.80054997693463</v>
+        <v>40.80055000267006</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>18.87924833249005</v>
+        <v>18.87924850059676</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.7194354089233886</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-7.716575221280719</v>
+        <v>-7.716575222402082</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>423.4800033664861</v>
+        <v>423.4800033664913</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>105</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>44.83298892803428</v>
+        <v>44.83298898393984</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.94496753696442</v>
+        <v>14.94496753906705</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>1.652978227471845</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2200767933635485</v>
+        <v>0.2200767929430366</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.56450169109296</v>
+        <v>43.56450169425095</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.28149536743916</v>
+        <v>19.28149537631569</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.303013117550042</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-32.16826832380364</v>
+        <v>-32.16826832436454</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>34.60645906812769</v>
+        <v>34.60645907460186</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>23.16194266961388</v>
+        <v>23.16194268226073</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>1.131861916142187</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.9714864024660281</v>
+        <v>-0.9714864025641683</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>420.9552504142662</v>
+        <v>420.9552504142663</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>20.6</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.01552331934433</v>
+        <v>46.01552343642798</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>31.42388569868365</v>
+        <v>31.42388569697798</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.297234138859749</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.05903288902009893</v>
+        <v>-0.05903288907616561</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.05244285035185</v>
+        <v>52.05244276950276</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.32498546010173</v>
+        <v>14.32498561309627</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.8870086207405919</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.06592740665419905</v>
+        <v>-0.06592740664018065</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>418.096633322559</v>
+        <v>418.0966333225593</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>27.9</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>58.02185295484748</v>
+        <v>58.02185301547959</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>33.46444781035556</v>
+        <v>33.46444828789287</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.6569260827724299</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1305307091159084</v>
+        <v>0.1305307096625666</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>417.0300614478011</v>
+        <v>417.0300614478006</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>95.3</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46.95832784018553</v>
+        <v>46.9583277952677</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.14819578256101</v>
+        <v>16.14819567465619</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.9585779500113204</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.01232788853658384</v>
+        <v>-0.01232788951776387</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.76454145564844</v>
+        <v>50.76454152172935</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.7843505183591</v>
+        <v>16.7843505133153</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.3573897523041073</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-7.074053210314013</v>
+        <v>-7.074053215920657</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.19414191516758</v>
+        <v>45.19414237410638</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.04572357239573</v>
+        <v>15.04572380911037</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.4909349330177543</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.07194540201247135</v>
+        <v>0.07194540166204805</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>409.5013779319261</v>
+        <v>409.501377931926</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>72.3</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.95340126627639</v>
+        <v>40.95340149212126</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.18801824634567</v>
+        <v>11.18801804442225</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.6941166408568731</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.001721243543431061</v>
+        <v>0.001721242562240599</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>405.7668505030771</v>
+        <v>405.7668505030769</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>1320</v>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.6927623976557</v>
+        <v>42.69276242979826</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.84534409261748</v>
+        <v>14.84534411993623</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.801490936700848</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-29.76113144276306</v>
+        <v>-29.76113143953908</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>34.60509977487797</v>
+        <v>34.60509980648187</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>19.12048977153857</v>
+        <v>19.12048992691503</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.4159241823051376</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.035418144819642</v>
+        <v>-1.035418144763577</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.49812336230035</v>
+        <v>45.49812333700504</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>27.58687336025805</v>
+        <v>27.58687340691277</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.5758813021426282</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.7939709835696824</v>
+        <v>-0.7939709833874606</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.50612330800531</v>
+        <v>42.50612332715931</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14.57200801933884</v>
+        <v>14.57200812170153</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.323207000271039</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.4250066180414273</v>
+        <v>-0.4250066179573262</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>392.377254626383</v>
+        <v>392.3772546263832</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>28.65</v>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.18286034170402</v>
+        <v>45.18286044364187</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>25.67240255104079</v>
+        <v>25.6724025824457</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.6074223752229556</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.06451365177692769</v>
+        <v>-0.06451365195914718</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>390.2728310370985</v>
+        <v>390.2728310370983</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>30</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>42.52632214637667</v>
+        <v>42.52632212983911</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>23.8084438356986</v>
+        <v>23.80844426445352</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.2760016557669057</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2107976707334412</v>
+        <v>-0.2107976702007946</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>389.7395986858372</v>
+        <v>389.7395986858371</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>96.8</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.94374794429225</v>
+        <v>46.94374804143175</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>23.23203544836022</v>
+        <v>23.23203546158773</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>2.394356646618488</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.488141154677681</v>
+        <v>-0.4881411547337399</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>38.7667950722707</v>
+        <v>38.76679507973338</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.32944365938136</v>
+        <v>14.329443800086</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.8711975893844028</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-2.435120414642589</v>
+        <v>-2.43512041436223</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>383.1059783254101</v>
+        <v>383.1059783254082</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>23.35</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.62074658498184</v>
+        <v>43.62074674051273</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.89318732373664</v>
+        <v>19.89318731380052</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.3726059287297239</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.003549353906182551</v>
+        <v>-0.003549353934215446</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.18433349368949</v>
+        <v>42.18433401015569</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.75847194874213</v>
+        <v>15.75847202731255</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>1.893205141494765</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.03121690177845093</v>
+        <v>0.0312169016663143</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>47.12077978379885</v>
+        <v>47.12077995647864</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.858961657514</v>
+        <v>15.85896168582643</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>1.021977447003947</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.2787151559195807</v>
+        <v>0.2787151557513823</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.47344038137979</v>
+        <v>42.47344037460877</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.58232395918393</v>
+        <v>14.58232411364901</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.3166152165986731</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.609391692654853</v>
+        <v>-0.6093916926688628</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>37.18816123069326</v>
+        <v>37.18816135388396</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>12.07695101147917</v>
+        <v>12.07695094821014</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.9405874457173088</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.04096474206647327</v>
+        <v>-0.04096474209450805</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>49.33974329928947</v>
+        <v>49.33974384251827</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.74981646654501</v>
+        <v>12.74981654281049</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.090391774357052</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.07473685371601593</v>
+        <v>0.07473685350576466</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>45.25107364755867</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.96701530784709</v>
+        <v>11.96701529272682</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.9145836072320699</v>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>360.630265720222</v>
+        <v>360.6302657202224</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>29.6</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.71398125194447</v>
+        <v>43.71398143467332</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>28.2789631250486</v>
+        <v>28.27896331628784</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.3198850128282118</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.5097748851956936</v>
+        <v>-0.5097748857003055</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>52.02334931825289</v>
+        <v>52.02334933548325</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>15.33728987789393</v>
+        <v>15.3372899158524</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.9363210577338612</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.1784425816242164</v>
+        <v>-0.1784425816802853</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>47.05615079953738</v>
+        <v>47.05615080826079</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>12.86243762083885</v>
+        <v>12.86243764715592</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1.031836050426445</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.03003712029178621</v>
+        <v>-0.03003712030580433</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>34.46768245186037</v>
+        <v>34.46768242375519</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>21.62161935883154</v>
+        <v>21.62161926232288</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.3255930846697945</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.9810392544465216</v>
+        <v>-0.9810392546707929</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>41.28618216047016</v>
+        <v>41.286182235447</v>
       </c>
       <c r="I119" s="2" t="n">
         <v>22.58005813368421</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-1.059877986352664</v>
+        <v>-1.059877986268552</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>346.6289936969455</v>
+        <v>346.6289936969458</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>552</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>32.80114911537436</v>
+        <v>32.80114909478654</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>25.47878003374003</v>
+        <v>25.47877986758669</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.7889413014151382</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-10.78640397941787</v>
+        <v>-10.78640397787603</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>346.1171034132664</v>
+        <v>346.117103413267</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>658</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>38.144356605822</v>
+        <v>38.14435685970098</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>18.34866394013269</v>
+        <v>18.3486639788642</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.5528298553140575</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-10.58078125485907</v>
+        <v>-10.58078125906411</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>40.13715421401604</v>
+        <v>40.13715419075945</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>26.04056375271445</v>
+        <v>26.04056384703697</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.4675703425590647</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-1.738908582821558</v>
+        <v>-1.73890858268139</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>33.33800350767541</v>
+        <v>33.33800360572013</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>21.1529667197476</v>
+        <v>21.15296723027645</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.3208995406694358</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1307541158674017</v>
+        <v>-0.130754116021589</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>339.7623188203085</v>
+        <v>339.7623188203084</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>2485</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>36.24415539481868</v>
+        <v>36.24415547593945</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.05611085237712</v>
+        <v>17.05611107746012</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.6665493535235427</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-72.378322888277</v>
+        <v>-72.37832287285798</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>44.80081517189156</v>
+        <v>44.80081537158254</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>21.22793878507043</v>
+        <v>21.22793890066867</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.3566738704796531</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.3813898514625451</v>
+        <v>-0.3813898516727934</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>336.071450184587</v>
+        <v>336.0714501845835</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>39.25</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>46.69614504010827</v>
+        <v>46.69614517997451</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>24.60999247572189</v>
+        <v>24.60999248085624</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.559050849247706</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.4433597942003087</v>
+        <v>-0.4433597948310773</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>48.49654713317842</v>
+        <v>48.49654668221875</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>26.23568160750991</v>
+        <v>26.23568177136339</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.7229004533125429</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.2086339165849429</v>
+        <v>-0.2086339157439215</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>39.21201539229097</v>
+        <v>39.21201537869883</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>39.44006992200192</v>
+        <v>39.44006990191089</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.3611933154721255</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.04698572663242062</v>
+        <v>-0.04698572661840489</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>46.26241983457757</v>
+        <v>46.26241991517747</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>20.38819440742837</v>
+        <v>20.38819438172888</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.4068279268948801</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.01530220828750788</v>
+        <v>-0.01530220837161154</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>43.49103697441258</v>
+        <v>43.49103687166795</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>21.93515516560038</v>
+        <v>21.93515518737183</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.9406557351678029</v>
@@ -7375,7 +7375,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>318.2159467733672</v>
+        <v>318.2159467733675</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>132.5</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>40.08789128202924</v>
+        <v>40.08789133738613</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>18.12854877997892</v>
+        <v>18.12854877625375</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.7457820561475852</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.6774596622616256</v>
+        <v>-0.6774596624018185</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>39.98870208253064</v>
+        <v>39.98870218995697</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>18.84562376362259</v>
+        <v>18.84562388060295</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>1.067377172472149</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>45.21985929034827</v>
+        <v>45.21985913733307</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>15.60296516683868</v>
+        <v>15.60296516469698</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>1.166918026883604</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.01658967304365588</v>
+        <v>-0.01658967302963796</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>40.9522286830726</v>
+        <v>40.95222853946479</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>9.041726764833657</v>
+        <v>9.041726765236072</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.6754955599063449</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.1124833877087631</v>
+        <v>-0.112483387148058</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>312.6154500175812</v>
+        <v>312.6154500175811</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>126.5</v>
@@ -7601,7 +7601,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>42.15149605938394</v>
+        <v>42.15149638627022</v>
       </c>
       <c r="I135" s="2" t="n">
         <v>22.55109918231157</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.2241112040057402</v>
+        <v>0.2241112037254092</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>34.90723867408931</v>
+        <v>34.90723870191779</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>18.66813297265396</v>
+        <v>18.66813305733337</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.6239895249919162</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-9.209237799383356</v>
+        <v>-9.209237799663757</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>36.31648534637781</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>16.99238719147626</v>
+        <v>16.9923872216764</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.5563339881438729</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>36.54343773163362</v>
+        <v>36.54343775574279</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>21.30710552451071</v>
+        <v>21.30710549836537</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.587065717657639</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.06420768011076455</v>
+        <v>-0.0642076800967486</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>308.6200057657519</v>
+        <v>308.620005765752</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>285</v>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>42.41851034562719</v>
+        <v>42.41851042043036</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>23.28586045338429</v>
+        <v>23.28586048285682</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.5368377387341955</v>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>71.72020701039389</v>
+        <v>71.72020710967315</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>35.4255338755151</v>
+        <v>35.42553406730605</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.3748124784192274</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>1.293941507637205</v>
+        <v>1.293941507259072</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>48.11622597173658</v>
+        <v>48.11622599654152</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>34.75818857851642</v>
+        <v>34.75818864270401</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.9760361368074193</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.03466425696527153</v>
+        <v>0.03466425713348431</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>49.90510680472491</v>
+        <v>49.90510682088961</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>7.824856905626152</v>
+        <v>7.824857077611317</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0.1349163518618457</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.09500959373120815</v>
+        <v>0.09500959352095439</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8025,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>26.52566125594602</v>
+        <v>26.52566136990285</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>20.61204392540877</v>
+        <v>20.61204405876214</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>3.303768547137214</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.08906290966559333</v>
+        <v>-0.08906290970764419</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>303.7095427076539</v>
+        <v>303.7095427076529</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>48.55</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>45.12940896571875</v>
+        <v>45.12940909562113</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>32.74603255703268</v>
+        <v>32.74603254879369</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.3148867151643849</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.2124683035509907</v>
+        <v>-0.2124683035089372</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>301.977586759729</v>
+        <v>301.9775867597292</v>
       </c>
       <c r="E145" s="2" t="n">
         <v>23.4</v>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>45.00692899520651</v>
+        <v>45.0069290220786</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>15.15324888643151</v>
+        <v>15.15324897002094</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>0.3849412171482139</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.1725489413493694</v>
+        <v>-0.172548941489537</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>35.85925626492845</v>
+        <v>35.85925574039123</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>20.02374682685656</v>
+        <v>20.02374712877121</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.1076071385109386</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.05906053245211407</v>
+        <v>-0.05906053180733162</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>49.77353636486961</v>
+        <v>49.77353636270834</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>8.128885948643941</v>
+        <v>8.128885963523164</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.1935526251940593</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-0.04347224576411257</v>
+        <v>-0.04347224590427845</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>296.8975362371145</v>
+        <v>296.8975362371175</v>
       </c>
       <c r="E148" s="2" t="n">
         <v>46.75</v>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>41.4204056291034</v>
+        <v>41.42040562173121</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>18.44463909828838</v>
+        <v>18.44463908276931</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.6609467672363187</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.5288311001509159</v>
+        <v>-0.5288311001789472</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>41.12978594250048</v>
+        <v>41.12978594712759</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>12.06298909456946</v>
+        <v>12.06298930781003</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.9274467510096661</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-0.3525618478144785</v>
+        <v>-0.3525618478425244</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>296.3041367113382</v>
+        <v>296.3041367113369</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>70.09999999999999</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>44.2070020880697</v>
+        <v>44.20700223073796</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>22.96913289819088</v>
+        <v>22.96913295142441</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>1.030264591323554</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-0.3598512033698795</v>
+        <v>-0.3598512033418489</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>40.07308485874667</v>
+        <v>40.07308489659935</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>17.43823331776018</v>
+        <v>17.43823342789699</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.8422830875681468</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-0.9934470875652517</v>
+        <v>-0.9934470879858004</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>284.7702084715133</v>
+        <v>284.7702084715136</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>121</v>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>40.69144192778509</v>
+        <v>40.69144247687861</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>10.46106485568293</v>
+        <v>10.46106499731905</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>0.6991558789717661</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>-0.07816682584715084</v>
+        <v>-0.07816682738902303</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>42.95621487538657</v>
+        <v>42.95621496818175</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>18.87372709272081</v>
+        <v>18.87372692092951</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>0.7090056162667296</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-0.1319111631483386</v>
+        <v>-0.131911163344575</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>280.2965353735184</v>
+        <v>280.2965353735182</v>
       </c>
       <c r="E154" s="2" t="n">
         <v>21</v>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>42.1239241355626</v>
+        <v>42.12392383994052</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>22.87752022600119</v>
+        <v>22.87752070589024</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>0.3534787185368163</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-0.2896702006471991</v>
+        <v>-0.2896702004789938</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>39.6148002307766</v>
+        <v>39.61480030889695</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>25.19994237806138</v>
+        <v>25.1999427324702</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>0.4364895101354573</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.3315006001746743</v>
+        <v>-0.3315006003568948</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>39.68589056294172</v>
+        <v>39.68589060420275</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>27.46677095935904</v>
+        <v>27.46677106499334</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.5311826590824896</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.1540717644629032</v>
+        <v>-0.1540717644909367</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>279.1573993072135</v>
+        <v>279.1573993072134</v>
       </c>
       <c r="E157" s="2" t="n">
         <v>506</v>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>34.38628919352949</v>
+        <v>34.38628919844953</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>25.44172929905206</v>
+        <v>25.44172949547693</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.9433047890469379</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-11.19757960341852</v>
+        <v>-11.19757960355864</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>278.7156761267041</v>
+        <v>278.7156761267043</v>
       </c>
       <c r="E158" s="2" t="n">
         <v>62.5</v>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>38.57114636043124</v>
+        <v>38.57114654720262</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>17.00430904526897</v>
+        <v>17.00430909719985</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>0.4906678605945939</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>48.63438052892165</v>
+        <v>48.63438039489932</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>15.86849364287716</v>
+        <v>15.86849372677129</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.5398913319699408</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.0001157414394342623</v>
+        <v>-0.0001157413673673266</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>270.8894687909352</v>
+        <v>270.8894687909349</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>24.3</v>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>30.26563021982662</v>
+        <v>30.26563025100695</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>30.43206383519636</v>
+        <v>30.43206383914686</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>1.015445135599569</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.5295592500593131</v>
+        <v>-0.529559250185469</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>44.44797291271735</v>
+        <v>44.44797300096231</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>19.55071237161446</v>
+        <v>19.55071224799088</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0.9975156135614801</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>1.208887145804618</v>
+        <v>1.208887143982405</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>44.18921235878728</v>
+        <v>44.18921251510305</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>30.02892536855035</v>
+        <v>30.02892563587927</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0.5530316288155732</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>-0.1073925067485231</v>
+        <v>-0.1073925068886953</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>266.9991357182951</v>
+        <v>266.9991357182953</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>69.7</v>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>42.04303886924224</v>
+        <v>42.04303897729769</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>12.61302014063267</v>
+        <v>12.61302037056084</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.5133152415675655</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.4631139357448564</v>
+        <v>-0.463113935464507</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>261.1377099704239</v>
+        <v>261.137709970424</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>17</v>
@@ -9141,7 +9141,7 @@
         <v>43.56934967830755</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>21.72267903549979</v>
+        <v>21.72267909474999</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0.4231097886927254</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-0.1927210375804652</v>
+        <v>-0.1927210375944803</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>41.26287254906178</v>
+        <v>41.26287263100131</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>24.39971206227656</v>
+        <v>24.39971206517438</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.1618492734142964</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.811324249869392</v>
+        <v>-0.8113242499394747</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>254.9434326349451</v>
+        <v>254.9434326349478</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>145</v>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>35.78959844632527</v>
+        <v>35.78959851585981</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>16.64564492531473</v>
+        <v>16.64564495371927</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>2.661199826696333</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-0.6206377110164869</v>
+        <v>-0.6206377117173378</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>254.4927161706858</v>
+        <v>254.492716170686</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>33.1</v>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>34.6251598259051</v>
+        <v>34.6251599291535</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>16.92674871439137</v>
+        <v>16.92674880889852</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>1.623376637883266</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>-0.3349663846693107</v>
+        <v>-0.3349663843048677</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>42.26366547083111</v>
+        <v>42.26366569492208</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>14.411787148842</v>
+        <v>14.41178715929721</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.6788931284466041</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-0.04019635407299349</v>
+        <v>-0.04019635379267639</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>253.6654058501041</v>
+        <v>253.6654058501034</v>
       </c>
       <c r="E169" s="2" t="n">
         <v>10.1</v>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>31.61901228660081</v>
+        <v>31.61901267519646</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>21.69638937731328</v>
+        <v>21.6963894989422</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.6712876448617833</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.06596331854070184</v>
+        <v>-0.06596331859676921</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>36.31031137732861</v>
+        <v>36.31031175099141</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>23.63371309787484</v>
+        <v>23.63371313066548</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>1.217667093448481</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>32.2963483544938</v>
+        <v>32.29634850506262</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>21.76880756728754</v>
+        <v>21.76880764123423</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>0.5836128294444668</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-2.672467454181327</v>
+        <v>-2.67246745460184</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>37.11442772296959</v>
+        <v>37.11442793514571</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>14.1864846754797</v>
+        <v>14.18648470185955</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>0.6296942351758886</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-0.318251912072479</v>
+        <v>-0.3182519123387971</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>46.94916684546967</v>
+        <v>46.94916685404001</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>21.27681164393977</v>
+        <v>21.27681182846094</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.6030249174302661</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-0.09725964537200715</v>
+        <v>-0.09725964540004595</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>42.71049317265466</v>
+        <v>42.71049338886675</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>11.00883952330089</v>
+        <v>11.00883952627608</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.9431047321954527</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.01298148074969813</v>
+        <v>-0.01298148081978319</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>42.77615640491777</v>
+        <v>42.77615641442416</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>14.77748003148125</v>
+        <v>14.7774800120553</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.5658145416494472</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-0.4894476922589372</v>
+        <v>-0.4894476923430287</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>245.4679475342551</v>
+        <v>245.467947534255</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>175.5</v>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>37.94728942390258</v>
+        <v>37.94728950903643</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>18.92669227254656</v>
+        <v>18.92669226333018</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>0.3759089749693111</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-2.46539990620103</v>
+        <v>-2.465399907182211</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>27.11047892733252</v>
+        <v>27.11047906312132</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>20.47570068806321</v>
+        <v>20.47570073894454</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>0.6010921123402219</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-6.46990537078559</v>
+        <v>-6.46990537008475</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>32.85390366730161</v>
+        <v>32.85390375888727</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>15.42151996035227</v>
+        <v>15.42152001754738</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>0.6758839147277594</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-0.4280460047918119</v>
+        <v>-0.4280460048198396</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>243.4491664624617</v>
+        <v>243.449166462462</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>12.35</v>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>34.64843540911045</v>
+        <v>34.64843553653535</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>26.10865068105657</v>
+        <v>26.10865071289857</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>0.8372262378649137</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.1412366375149289</v>
+        <v>-0.1412366375009134</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>44.90161179084208</v>
+        <v>44.90161186993942</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>20.67178818163792</v>
+        <v>20.67178816580527</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.3675830663431973</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.07428957918098877</v>
+        <v>-0.0742895791669716</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>234.3314022872488</v>
+        <v>234.3314022872486</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>122.5</v>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>31.50091424031265</v>
+        <v>31.50091411961897</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>18.64861910515735</v>
+        <v>18.64861920093104</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.6995487552397942</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-1.253958401043907</v>
+        <v>-1.25395840076356</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>36.27223409381593</v>
+        <v>36.27223410410438</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>17.12561241053512</v>
+        <v>17.12561241619483</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>0.4458375982733768</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-2.458047285412078</v>
+        <v>-2.45804728569239</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>38.20386854643435</v>
+        <v>38.2038685348856</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>14.8898037765888</v>
+        <v>14.88980382448979</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>1.610769181350594</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.07063536610959187</v>
+        <v>-0.07063536616565769</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>45.68216898059695</v>
+        <v>45.68216891293588</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>12.77591193674697</v>
+        <v>12.7759117922047</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>0.538089623574656</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.01685476061828062</v>
+        <v>-0.01685476060426169</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>37.55449897149003</v>
+        <v>37.55449914756273</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>18.22382612606441</v>
+        <v>18.22382613808336</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>0.2708359040685407</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.3343924054245776</v>
+        <v>-0.3343924058450856</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>40.03095410627439</v>
+        <v>40.03095415657278</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>16.14624821832562</v>
+        <v>16.14624823429052</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>0.6343840958692697</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.06511834133966743</v>
+        <v>0.06511834136769434</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>220.1221696028694</v>
+        <v>220.1221696028697</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>1875</v>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>33.40256420846914</v>
+        <v>33.40256423214602</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>19.18478578428466</v>
+        <v>19.18478589008134</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>0.6034932161235916</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>-59.95794090406483</v>
+        <v>-59.95794090883051</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>40.04396434971517</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>17.95738356000584</v>
+        <v>17.95738363622672</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>1.386520689639467</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-0.8065054652678962</v>
+        <v>-0.8065054653379811</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>218.1107700640053</v>
+        <v>218.1107700639945</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>10.1</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>35.42512628691269</v>
+        <v>35.4251277561557</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>19.89190512278722</v>
+        <v>19.89190508782134</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>1.365601782807376</v>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>29.75137521442187</v>
+        <v>29.75137530577514</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>21.31517478675254</v>
+        <v>21.31517491448238</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>1.364607391014835</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.03545359826803218</v>
+        <v>-0.03545359838016782</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>41.92510340331148</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>8.89507252214039</v>
+        <v>8.895072530994257</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>0.6087048669348798</v>
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>211.0609025523658</v>
+        <v>211.0609025523667</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>13.6</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>42.1181479629215</v>
+        <v>42.11814821506448</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>28.04482012027632</v>
+        <v>28.04482026905729</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.8776351739970727</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.02153246586944911</v>
+        <v>-0.02153246600961931</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>29.69625802784807</v>
+        <v>29.69625809404347</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>17.2544822961281</v>
+        <v>17.25448233980713</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.8793007223637715</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-13.59493596393628</v>
+        <v>-13.59493596603884</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10728,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>49.76629574298865</v>
+        <v>49.76629573786134</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>9.843980971446953</v>
+        <v>9.843981127105497</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.3124306933012636</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.01584129270490431</v>
+        <v>-0.01584129267686996</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>29.07324459699581</v>
+        <v>29.07324482092912</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>17.45953420291558</v>
+        <v>17.45953443798734</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>1.191825297424593</v>
@@ -10820,7 +10820,7 @@
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>206.8341309125609</v>
+        <v>206.8341309125601</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>257.5</v>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>31.83071650765889</v>
+        <v>31.83071660974677</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>24.31749290239766</v>
+        <v>24.31749294349693</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>1.453741568746823</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-1.021260841762328</v>
+        <v>-1.021260842042611</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>205.7695215637023</v>
+        <v>205.7695215637024</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>127</v>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>40.5497257054175</v>
+        <v>40.54972538796808</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>25.19556101229656</v>
+        <v>25.19556122046001</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>0.4339474726439501</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-1.331130967613963</v>
+        <v>-1.331130964950743</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v/>
       </c>
       <c r="D198" s="2" t="n">
-        <v>204.3064078510569</v>
+        <v>204.3064078510562</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>43.7</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>34.59493975248725</v>
+        <v>34.59493966633494</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>24.23847925939168</v>
+        <v>24.2384794361571</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>1.74943875279823</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.3696334419765906</v>
+        <v>-0.3696334415280431</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>38.17613152238103</v>
+        <v>38.17613172392186</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>12.504059455297</v>
+        <v>12.5040593869559</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>1.11227302975568</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.0812217717348927</v>
+        <v>-0.08122177179095993</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>203.36029170089</v>
+        <v>203.3602917009013</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>101.5</v>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>43.78281926148697</v>
+        <v>43.78281931874177</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>13.1903828789966</v>
+        <v>13.19038307358292</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>1.003635007966831</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.9586145810221249</v>
+        <v>-0.9586145815968179</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>38.12901416824258</v>
+        <v>38.12901418538552</v>
       </c>
       <c r="I201" s="2" t="n">
         <v>15.91976675104232</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.568109752704507</v>
+        <v>-0.5681097529287815</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>201.6536252858016</v>
+        <v>201.6536252858007</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>27.4</v>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>45.4108099596361</v>
+        <v>45.41081057484209</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>16.89554902016313</v>
+        <v>16.89554930044146</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.4368586007544787</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.05163228827759329</v>
+        <v>-0.05163228810938675</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>201.5357985315075</v>
+        <v>201.5357985315101</v>
       </c>
       <c r="E203" s="2" t="n">
         <v>15.05</v>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>40.87059493352152</v>
+        <v>40.87059458791568</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>20.54309259292475</v>
+        <v>20.54309267753468</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.6830904437458366</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.1667830760263025</v>
+        <v>-0.1667830758440816</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>32.7649194007445</v>
+        <v>32.76491954376111</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>14.97582631725234</v>
+        <v>14.97582629839059</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.7791955277801752</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>0.02508583559068056</v>
+        <v>0.02508583552059385</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>34.94219305006051</v>
+        <v>34.94219307044402</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>12.78573057534511</v>
+        <v>12.78573059470065</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.7978780017295284</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.1089543774029984</v>
+        <v>-0.1089543774071194</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>171.8905057833278</v>
+        <v>171.8905057833279</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>216.5</v>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>35.58209198654144</v>
+        <v>35.58209195185304</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>11.74076534139772</v>
+        <v>11.7407653747303</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.7176931811954497</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-2.250689611536916</v>
+        <v>-2.25068961097622</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>169.5441971510585</v>
+        <v>169.5441971510586</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>1985</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>30.93019158376825</v>
+        <v>30.93019162565525</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>15.04258832686585</v>
+        <v>15.04258836930488</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.7167606951982991</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-42.3791598793313</v>
+        <v>-42.37915988213445</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>34.32016112169505</v>
+        <v>34.32016111398879</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>15.4617116513759</v>
+        <v>15.46171158417576</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>1.195441671485979</v>
@@ -11509,7 +11509,7 @@
         <v/>
       </c>
       <c r="D209" s="2" t="n">
-        <v>156.5412790301296</v>
+        <v>156.5412790301291</v>
       </c>
       <c r="E209" s="2" t="n">
         <v>46.55</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>37.72991968255424</v>
+        <v>37.72991986239111</v>
       </c>
       <c r="I209" s="2" t="n">
         <v>13.7877341762093</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>-0.2415125586662279</v>
+        <v>-0.2415125582737533</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>155.5360508976387</v>
+        <v>155.5360508976394</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>19.45</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>33.48222260339503</v>
+        <v>33.48222316731754</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>13.6916148464424</v>
+        <v>13.69161488472971</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.909096968232677</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>-0.02881198529752843</v>
+        <v>-0.02881198585820594</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>151.7913135702539</v>
+        <v>151.7913135702535</v>
       </c>
       <c r="E211" s="2" t="n">
         <v>18.65</v>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>40.51224270789649</v>
+        <v>40.51224274728654</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>15.20978249059819</v>
+        <v>15.2097826985192</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>1.253794165314384</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.08713639356822193</v>
+        <v>-0.08713639368035925</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>151.452692072794</v>
+        <v>151.4526920727947</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>11.3</v>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>41.71326264412038</v>
+        <v>41.71326257713537</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>21.42031262661029</v>
+        <v>21.42031262795538</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.4663426785341764</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>-0.03884986189098216</v>
+        <v>-0.03884986187696354</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>151.1346686285431</v>
+        <v>151.1346686285433</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>8.359999999999999</v>
@@ -11735,7 +11735,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>51.99658601934822</v>
+        <v>51.99658606498915</v>
       </c>
       <c r="I213" s="2" t="n">
         <v>8.007015155910981</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.08977249224330441</v>
+        <v>-0.08977249222928657</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>141.4618022618818</v>
+        <v>141.4618022618778</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>48.55</v>
@@ -11788,7 +11788,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>42.81902463691465</v>
+        <v>42.81902535579375</v>
       </c>
       <c r="I214" s="2" t="n">
         <v>17.96461424663834</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-0.1226661299937629</v>
+        <v>-0.1226661301619596</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>132.8778024867321</v>
+        <v>132.8778024867017</v>
       </c>
       <c r="E215" s="2" t="n">
         <v>27</v>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>47.62007341270316</v>
+        <v>47.62007374058775</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>28.17935813671524</v>
+        <v>28.17935821737571</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.6065957883378548</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.1211442375286851</v>
+        <v>-0.1211442374165497</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>33.88419273611329</v>
+        <v>33.88419279058886</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>11.86121316454971</v>
+        <v>11.86121326248999</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.854472247258505</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.1744030719242865</v>
+        <v>-0.1744030720924865</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>34.60723796376416</v>
+        <v>34.60723810255489</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>12.0973245286948</v>
+        <v>12.09732459177549</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.9908090452175952</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.1757430825772903</v>
+        <v>-0.1757430827034418</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>97.07344792161044</v>
+        <v>97.07344792161071</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>25.1</v>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>34.66364054781334</v>
+        <v>34.66364067664803</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>11.75387960157311</v>
+        <v>11.75387965436808</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>1.250424561940035</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-0.07618605884692597</v>
+        <v>-0.07618605886094751</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>96.92668893345795</v>
+        <v>96.92668893345814</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>41.1</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>48.81419964910501</v>
+        <v>48.81419969277032</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>8.063747102044751</v>
+        <v>8.063747045188196</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>0.3986062069629861</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.1162316402398686</v>
+        <v>-0.1162316403520098</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>94.09835563570252</v>
+        <v>94.09835563570259</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>37.65</v>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>39.71191339436376</v>
+        <v>39.71191346150039</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>18.71793942659582</v>
+        <v>18.71793930353705</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.7383509692574197</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>0.008000376745471577</v>
+        <v>0.00800037649316454</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>90.44781160837931</v>
+        <v>90.44781160837911</v>
       </c>
       <c r="E221" s="2" t="n">
         <v>49</v>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>38.24716063154376</v>
+        <v>38.247160945636</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>19.46046001587775</v>
+        <v>19.46046009986164</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>0.4557696620385697</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.5032432027588976</v>
+        <v>-0.5032432030252232</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>79.64764953785722</v>
+        <v>79.64764953785699</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>55.6</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>39.40920161989192</v>
+        <v>39.40920200004089</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>16.93144658649074</v>
+        <v>16.93144663607754</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>0.6064323707399148</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>-0.2807669631547008</v>
+        <v>-0.2807669633509393</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v/>
       </c>
       <c r="D223" s="2" t="n">
-        <v>52.84811232625699</v>
+        <v>52.84811232625704</v>
       </c>
       <c r="E223" s="2" t="n">
         <v>13.85</v>
@@ -12265,10 +12265,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>50.61587106294895</v>
+        <v>50.61587106936313</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>12.45179203250198</v>
+        <v>12.4517919801226</v>
       </c>
       <c r="J223" s="2" t="n">
         <v>0.609568230403519</v>
@@ -12283,7 +12283,7 @@
         <v>-1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>-0.124896585787634</v>
+        <v>-0.1248965857736161</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v/>
       </c>
       <c r="D224" s="2" t="n">
-        <v>45.94887158169266</v>
+        <v>45.94887158169333</v>
       </c>
       <c r="E224" s="2" t="n">
         <v>35.6</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>33.19459577390771</v>
+        <v>33.1945957585519</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>16.82299913060806</v>
+        <v>16.82299909071572</v>
       </c>
       <c r="J224" s="2" t="n">
         <v>1.166614109881752</v>
@@ -12336,7 +12336,7 @@
         <v>-1</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>-0.2017227895015008</v>
+        <v>-0.2017227892772366</v>
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>
